--- a/frontend/public/plantilla_evaluadores.xlsx
+++ b/frontend/public/plantilla_evaluadores.xlsx
@@ -64,8 +64,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001E3A5F"/>
-        <bgColor rgb="001E3A5F"/>
+        <fgColor rgb="00065F46"/>
+        <bgColor rgb="00065F46"/>
       </patternFill>
     </fill>
     <fill>
@@ -497,7 +497,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Completa los datos de cada persona. El correo debe corresponder a un usuario ya registrado en el sistema con el rol indicado.</t>
+          <t>Completa una fila por cada persona. Todos los campos son obligatorios. El correo debe ser de un usuario ya registrado con ese mismo rol.</t>
         </is>
       </c>
     </row>
@@ -511,22 +511,22 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>nombre*</t>
+          <t>nombre</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>apellidos*</t>
+          <t>apellidos</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>correo*</t>
+          <t>correo</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>rol*</t>
+          <t>rol</t>
         </is>
       </c>
     </row>

--- a/frontend/public/plantilla_evaluadores.xlsx
+++ b/frontend/public/plantilla_evaluadores.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Evaluadores" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Instrucciones" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,23 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="001E3A5F"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <color rgb="001E40AF"/>
-      <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
@@ -44,23 +35,20 @@
       <sz val="10"/>
     </font>
     <font>
-      <i val="1"/>
-      <color rgb="0094A3B8"/>
-      <sz val="9"/>
+      <b val="1"/>
+      <color rgb="001E3A5F"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E8F0FE"/>
-        <bgColor rgb="00E8F0FE"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -101,18 +89,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -478,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -490,148 +475,190 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PLANTILLA PARA CARGA MASIVA DE EVALUADORES Y COLABORADORES - ECOE</t>
+          <t>nombre</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>apellidos</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>correo</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>rol</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Completa una fila por cada persona. Todos los campos son obligatorios. El correo debe ser de un usuario ya registrado con ese mismo rol.</t>
+          <t>Laura</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Martinez Contreras</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>laura.martinez@ejemplo.cl</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>evaluador</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Roles validos: evaluador | coeditor_docente | coordinador_operativo | cronometrador</t>
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Pedro</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Gonzalez Silva</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>pedro.gonzalez@ejemplo.cl</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>evaluador</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>nombre</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>apellidos</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>correo</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>rol</t>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Sofia</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Vargas Lopez</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>sofia.vargas@ejemplo.cl</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>coordinador_operativo</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>Laura</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Martinez Contreras</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>laura.martinez@ejemplo.cl</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>evaluador</t>
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Tomas</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Herrera Diaz</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>tomas.herrera@ejemplo.cl</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>cronometrador</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="80" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Como usar esta plantilla</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>1. La pestana 'Evaluadores' tiene los encabezados en la FILA 1. No agregues filas antes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>2. Completa una fila por cada persona a partir de la fila 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>3. Todos los campos son obligatorios.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Pedro</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>Gonzalez Silva</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>pedro.gonzalez@ejemplo.cl</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>evaluador</t>
+          <t>4. El correo debe ser de un usuario YA REGISTRADO en el sistema con el mismo rol.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>Sofia</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Vargas Lopez</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>sofia.vargas@ejemplo.cl</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>coordinador_operativo</t>
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>5. Roles validos: evaluador | coeditor_docente | coordinador_operativo | cronometrador.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Tomas</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>Herrera Diaz</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>tomas.herrera@ejemplo.cl</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>cronometrador</t>
+          <t>6. Elimina las filas de ejemplo antes de importar.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>Elimina las filas de ejemplo antes de importar. Guarda como .xlsx o .csv (UTF-8).</t>
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>7. Guarda como .xlsx o .csv (UTF-8) y subelo en la pagina de Evaluadores.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A2:D2"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>